--- a/data/metadata_raw/agricultural_output.xlsx
+++ b/data/metadata_raw/agricultural_output.xlsx
@@ -521,7 +521,7 @@
     <t>2022-08-18</t>
   </si>
   <si>
-    <t>2024-08-23</t>
+    <t>2025-09-16</t>
   </si>
   <si>
     <t>1.03.02.0001</t>
